--- a/ig/DM-OCTOBRE-2024/CodeSystem-TRE-G100-Specialite-AM.xlsx
+++ b/ig/DM-OCTOBRE-2024/CodeSystem-TRE-G100-Specialite-AM.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="222">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20231215120000</t>
+    <t>20241025120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-15T12:00:00+01:00</t>
+    <t>2024-10-25T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -292,6 +292,18 @@
     <t>Sage-Femme</t>
   </si>
   <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>Spécialité médecine générale</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>Reconnaissance spécialité médecine générale</t>
+  </si>
+  <si>
     <t>24</t>
   </si>
   <si>
@@ -472,6 +484,78 @@
     <t>Chirurgien dentiste spécialité Médecine bucco-dentaire</t>
   </si>
   <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>Transporteur sanitaire</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>Taxis</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>Autres transporteurs</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>Société</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>Artisan</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>Société CRAMIF Île de France</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>Orthèses et Prothèses externes non orthopédiques</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>Optique médicale</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>Audioprothèse</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>Prothèses oculaires et faciales</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>Podo-Orthèses</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>Orthoprothèses</t>
+  </si>
+  <si>
     <t>69</t>
   </si>
   <si>
@@ -578,6 +662,18 @@
   </si>
   <si>
     <t>Infirmier exerçant en pratiques avancées</t>
+  </si>
+  <si>
+    <t>87</t>
+  </si>
+  <si>
+    <t>Ergothérapeute</t>
+  </si>
+  <si>
+    <t>88</t>
+  </si>
+  <si>
+    <t>Psychomotricien</t>
   </si>
   <si>
     <t>99</t>
@@ -957,7 +1053,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D87"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1814,6 +1910,198 @@
       </c>
       <c r="D71" s="2"/>
     </row>
+    <row r="72">
+      <c r="A72" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="C72" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="D72" s="2"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="C73" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="D73" s="2"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="C74" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="D74" s="2"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="C75" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="D75" s="2"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="C76" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="D76" s="2"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="C77" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="D77" s="2"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="C78" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="D78" s="2"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="C79" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="D79" s="2"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="C80" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="D80" s="2"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="C81" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="D81" s="2"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="C82" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="D82" s="2"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="C83" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="D83" s="2"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="C84" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="D84" s="2"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="C85" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="D85" s="2"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="C86" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="D86" s="2"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="C87" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="D87" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
